--- a/data/trans_orig/IP16A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>18248</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41661</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72051</t>
+          <t>71847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78471</t>
+          <t>78618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76605</t>
+          <t>76752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151368</t>
+          <t>151206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161883</t>
+          <t>161437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>28607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34540</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56319</t>
+          <t>56268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>25313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113010</t>
+          <t>112934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121618</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125637</t>
+          <t>126187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136509</t>
+          <t>137008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243444</t>
+          <t>243185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256563</t>
+          <t>256555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80654</t>
+          <t>80539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86867</t>
+          <t>86863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91764</t>
+          <t>91794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99813</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175916</t>
+          <t>176595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185652</t>
+          <t>185643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67938</t>
+          <t>68813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74530</t>
+          <t>74528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>135791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>143741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145670</t>
+          <t>146094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155281</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285972</t>
+          <t>285950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>297460</t>
+          <t>297912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79730</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80499</t>
+          <t>80870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162354</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167789</t>
+          <t>167797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>48887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55701</t>
+          <t>55726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121790</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>126768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>111647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120221</t>
+          <t>120071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235753</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245858</t>
+          <t>246001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24531</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114057</t>
+          <t>113271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120843</t>
+          <t>120203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111487</t>
+          <t>111420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118345</t>
+          <t>118266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228626</t>
+          <t>228690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237759</t>
+          <t>237907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86008</t>
+          <t>86016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170335</t>
+          <t>169891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176942</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170272</t>
+          <t>170673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>179214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345182</t>
+          <t>344235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>355181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1245</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4439</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4117</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18915</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16169</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20803</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18248</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17609</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18915</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16141</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36528</t>
+          <t>36331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10908</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4831</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2089</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8860</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9484</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6237</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2926</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10917</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81432</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76761</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84567</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>75876</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71847</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>78618</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>71223</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78334</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>81432</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76752</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>84743</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151206</t>
+          <t>151782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161437</t>
+          <t>161440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6452</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4002</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3919</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6659</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32381</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28814</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34542</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21351</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18549</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18632</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,62%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32381</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28607</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34536</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>81,12%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>81</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49595</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56268</t>
+          <t>55960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16367</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4042</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12371</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12252</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6185</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17006</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132728</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>126826</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>137301</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>118030</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>112934</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>121263</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>113053</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>121407</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132728</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>126187</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>137008</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243185</t>
+          <t>242943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256555</t>
+          <t>256204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2908</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4768</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14592</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21202</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17813</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18344</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>81,24%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16893</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14877</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>85,01%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34843</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8255</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3740</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7697</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9240</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92779</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100153</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84496</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80539</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>86863</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80368</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>86819</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>91794</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>99884</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176595</t>
+          <t>176130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185643</t>
+          <t>186021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5372</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1445</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4366</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37470</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34061</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38803</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>34959</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31847</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>32038</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37470</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34055</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38802</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>86,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>100</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68813</t>
+          <t>68281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74528</t>
+          <t>74535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11462</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11430</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11801</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11872</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>151896</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>146504</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>140657</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>135791</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143741</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>135420</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>143879</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>151896</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>146094</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>155050</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285950</t>
+          <t>286011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>297912</t>
+          <t>297183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,102 +3934,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>765</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3971</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,88%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5043</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5508</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5278</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14926</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11720</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11493</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>73,24%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7895</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4637</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>52,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4277,67 +4277,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5517</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3412</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2876</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4750</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4385,74 +4385,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84210</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80103</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>82069</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>79567</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80103</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84210</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>80870</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162428</t>
+          <t>162545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167797</t>
+          <t>168014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4166</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7689</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24962</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21090</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27516</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>28087</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24626</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25299</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,87%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24962</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>21181</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27108</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>77</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>48788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>55658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11480</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5733</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11629</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>117066</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>111796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>120178</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>125081</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>121728</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>126768</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>121907</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>126755</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>117066</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>111647</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>120071</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236650</t>
+          <t>236501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>246375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4213</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5756</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13688</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9911</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15667</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28918</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,107 +5875,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8164</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2475</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7572</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>11877</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,47%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>12177</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104032</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>99748</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106354</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>118368</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113271</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120203</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115922</t>
+          <t>90458</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111420</t>
+          <t>86437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118266</t>
+          <t>92039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>194490</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>188719</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>197657</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>234291</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>228690</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>237907</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,107 +6218,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1572</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2299</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41220</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39724</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>40161</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38955</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>40527</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>46511</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>121</t>
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>83281</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86016</t>
+          <t>81348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7824</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159783</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>154774</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162512</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>174819</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>169891</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>176897</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>176120</t>
+          <t>140400</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170673</t>
+          <t>136107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179214</t>
+          <t>142229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>350939</t>
+          <t>300183</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344235</t>
+          <t>293932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
